--- a/exports/trend_1d/LICHSGFIN_full_report.xlsx
+++ b/exports/trend_1d/LICHSGFIN_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q87"/>
+  <dimension ref="A1:U87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>11.3</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42075</v>
+        <v>42076</v>
       </c>
       <c r="H2" t="n">
-        <v>456.3</v>
+        <v>438.25</v>
       </c>
       <c r="I2" t="n">
         <v>441.5134371724803</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.29</v>
+        <v>-4.24</v>
       </c>
       <c r="L2" t="n">
-        <v>4.84</v>
+        <v>4.86</v>
       </c>
       <c r="M2" t="n">
         <v>2.11</v>
       </c>
       <c r="N2" t="n">
-        <v>3.26</v>
+        <v>3.96</v>
       </c>
       <c r="O2" t="n">
         <v>2.72</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>13.37</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42173</v>
+        <v>42174</v>
       </c>
       <c r="H3" t="n">
-        <v>420.1</v>
+        <v>431.25</v>
       </c>
       <c r="I3" t="n">
         <v>424.3058812998401</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K3" t="n">
-        <v>4.14</v>
+        <v>1.6</v>
       </c>
       <c r="L3" t="n">
         <v>6.45</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42089</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>4</v>
+      </c>
+      <c r="U3" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>9.949999999999999</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42236</v>
+        <v>42237</v>
       </c>
       <c r="H4" t="n">
-        <v>463.65</v>
+        <v>452.6</v>
       </c>
       <c r="I4" t="n">
         <v>461.4252314034504</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K4" t="n">
-        <v>7.51</v>
+        <v>4.95</v>
       </c>
       <c r="L4" t="n">
         <v>2.5</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42180</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -705,22 +764,22 @@
         <v>10.57</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42278</v>
+        <v>42282</v>
       </c>
       <c r="H5" t="n">
-        <v>454.5</v>
+        <v>474.65</v>
       </c>
       <c r="I5" t="n">
         <v>463.8558651267811</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.42</v>
+        <v>-4.87</v>
       </c>
       <c r="L5" t="n">
-        <v>3.27</v>
+        <v>5.17</v>
       </c>
       <c r="M5" t="n">
         <v>2.93</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42243</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>13.86</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42383</v>
+        <v>42384</v>
       </c>
       <c r="H6" t="n">
-        <v>476.45</v>
+        <v>457.95</v>
       </c>
       <c r="I6" t="n">
         <v>468.9201179932456</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="K6" t="n">
-        <v>0.38</v>
+        <v>-3.52</v>
       </c>
       <c r="L6" t="n">
         <v>7.29</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42306</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>4</v>
+      </c>
+      <c r="U6" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>12.34</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42430</v>
+        <v>42431</v>
       </c>
       <c r="H7" t="n">
-        <v>430.7</v>
+        <v>444</v>
       </c>
       <c r="I7" t="n">
         <v>432.2196423575955</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K7" t="n">
-        <v>5.95</v>
+        <v>3.05</v>
       </c>
       <c r="L7" t="n">
         <v>5.25</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42397</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>12.19</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42494</v>
+        <v>42495</v>
       </c>
       <c r="H8" t="n">
-        <v>442.85</v>
+        <v>440.9</v>
       </c>
       <c r="I8" t="n">
         <v>442.3441222628487</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.26</v>
+        <v>-0.7</v>
       </c>
       <c r="L8" t="n">
         <v>3.23</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42460</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -933,22 +1040,22 @@
         <v>7.24</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42520</v>
+        <v>42521</v>
       </c>
       <c r="H9" t="n">
-        <v>459.85</v>
+        <v>462.25</v>
       </c>
       <c r="I9" t="n">
         <v>460.057565392617</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K9" t="n">
-        <v>-4.3</v>
+        <v>-4.84</v>
       </c>
       <c r="L9" t="n">
-        <v>5.13</v>
+        <v>5.28</v>
       </c>
       <c r="M9" t="n">
         <v>1.08</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42516</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>7.58</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42676</v>
+        <v>42677</v>
       </c>
       <c r="H10" t="n">
-        <v>564.7</v>
+        <v>541.75</v>
       </c>
       <c r="I10" t="n">
         <v>550.6372262453211</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="K10" t="n">
-        <v>22.16</v>
+        <v>17.2</v>
       </c>
       <c r="L10" t="n">
         <v>1.78</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>105</v>
+        <v>106</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42551</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>6</v>
+      </c>
+      <c r="U10" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="11">
@@ -1047,22 +1178,22 @@
         <v>10.85</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42704</v>
+        <v>42705</v>
       </c>
       <c r="H11" t="n">
-        <v>555.9</v>
+        <v>562.55</v>
       </c>
       <c r="I11" t="n">
         <v>561.6377020006233</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K11" t="n">
-        <v>-2.61</v>
+        <v>-3.84</v>
       </c>
       <c r="L11" t="n">
-        <v>4.2</v>
+        <v>4.73</v>
       </c>
       <c r="M11" t="n">
         <v>2.35</v>
@@ -1077,7 +1208,19 @@
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42698</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,22 +1247,22 @@
         <v>10.93</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42738</v>
+        <v>42739</v>
       </c>
       <c r="H12" t="n">
-        <v>522.8</v>
+        <v>508.45</v>
       </c>
       <c r="I12" t="n">
         <v>514.277670623007</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K12" t="n">
-        <v>-7.07</v>
+        <v>-9.619999999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>9.34</v>
+        <v>9.81</v>
       </c>
       <c r="M12" t="n">
         <v>1.49</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42733</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>10.87</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42762</v>
+        <v>42765</v>
       </c>
       <c r="H13" t="n">
-        <v>549.25</v>
+        <v>551</v>
       </c>
       <c r="I13" t="n">
         <v>550.6762492626044</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="K13" t="n">
-        <v>-8.02</v>
+        <v>-8.369999999999999</v>
       </c>
       <c r="L13" t="n">
         <v>9.06</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42760</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>8.07</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>42877</v>
+        <v>42878</v>
       </c>
       <c r="H14" t="n">
-        <v>667.75</v>
+        <v>662</v>
       </c>
       <c r="I14" t="n">
         <v>663.5893601935323</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="K14" t="n">
-        <v>21.19</v>
+        <v>20.15</v>
       </c>
       <c r="L14" t="n">
         <v>3.88</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>76</v>
+        <v>77</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>42789</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>4</v>
+      </c>
+      <c r="U14" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="15">
@@ -1275,28 +1454,28 @@
         <v>7.31</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>42885</v>
+        <v>42886</v>
       </c>
       <c r="H15" t="n">
-        <v>703.35</v>
+        <v>725.6</v>
       </c>
       <c r="I15" t="n">
         <v>709.4597761807728</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K15" t="n">
-        <v>-6.25</v>
+        <v>-9.609999999999999</v>
       </c>
       <c r="L15" t="n">
-        <v>6.6</v>
+        <v>10.3</v>
       </c>
       <c r="M15" t="n">
-        <v>0.15</v>
+        <v>0.45</v>
       </c>
       <c r="N15" t="n">
-        <v>2.61</v>
+        <v>3.16</v>
       </c>
       <c r="O15" t="n">
         <v>-0.86</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>42880</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>8.35</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>42926</v>
+        <v>42927</v>
       </c>
       <c r="H16" t="n">
-        <v>734.7</v>
+        <v>716.6</v>
       </c>
       <c r="I16" t="n">
         <v>725.5897526761169</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K16" t="n">
-        <v>1.25</v>
+        <v>-1.24</v>
       </c>
       <c r="L16" t="n">
         <v>2.87</v>
@@ -1353,7 +1544,7 @@
         <v>1.02</v>
       </c>
       <c r="N16" t="n">
-        <v>2.16</v>
+        <v>2.46</v>
       </c>
       <c r="O16" t="n">
         <v>3.16</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>42915</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>8.82</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>43014</v>
+        <v>43017</v>
       </c>
       <c r="H17" t="n">
-        <v>654.55</v>
+        <v>656.4</v>
       </c>
       <c r="I17" t="n">
         <v>654.6776060466179</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="K17" t="n">
-        <v>8.66</v>
+        <v>8.4</v>
       </c>
       <c r="L17" t="n">
         <v>4.42</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>42943</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>4</v>
+      </c>
+      <c r="U17" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -1446,22 +1661,22 @@
         <v>6.87</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>43032</v>
+        <v>43033</v>
       </c>
       <c r="H18" t="n">
-        <v>625.35</v>
+        <v>609.9</v>
       </c>
       <c r="I18" t="n">
         <v>616.6144927672319</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K18" t="n">
-        <v>-4.73</v>
+        <v>-7.08</v>
       </c>
       <c r="L18" t="n">
-        <v>5.19</v>
+        <v>8.5</v>
       </c>
       <c r="M18" t="n">
         <v>0.91</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>43034</v>
+      </c>
+      <c r="S18" t="b">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>9.57</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>43105</v>
+        <v>43108</v>
       </c>
       <c r="H19" t="n">
-        <v>562.75</v>
+        <v>575.4</v>
       </c>
       <c r="I19" t="n">
         <v>574.3619886553364</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="K19" t="n">
-        <v>7.73</v>
+        <v>5.66</v>
       </c>
       <c r="L19" t="n">
         <v>3.53</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>43034</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>4</v>
+      </c>
+      <c r="U19" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>6.38</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43125</v>
+        <v>43129</v>
       </c>
       <c r="H20" t="n">
-        <v>547.35</v>
+        <v>539.3</v>
       </c>
       <c r="I20" t="n">
         <v>540.8156404451262</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="K20" t="n">
-        <v>-4.87</v>
+        <v>-6.27</v>
       </c>
       <c r="L20" t="n">
         <v>7.26</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43125</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>8.81</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43182</v>
+        <v>43185</v>
       </c>
       <c r="H21" t="n">
-        <v>511.35</v>
+        <v>535.6</v>
       </c>
       <c r="I21" t="n">
         <v>520.7410656716735</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="K21" t="n">
-        <v>5.18</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="L21" t="n">
         <v>2.87</v>
@@ -1638,7 +1889,7 @@
         <v>1.65</v>
       </c>
       <c r="N21" t="n">
-        <v>4.24</v>
+        <v>4.74</v>
       </c>
       <c r="O21" t="n">
         <v>-1.47</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43153</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,22 +1937,22 @@
         <v>9.949999999999999</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43224</v>
+        <v>43227</v>
       </c>
       <c r="H22" t="n">
-        <v>509.25</v>
+        <v>507.55</v>
       </c>
       <c r="I22" t="n">
         <v>509.0396443963302</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="K22" t="n">
-        <v>-4.92</v>
+        <v>-5.24</v>
       </c>
       <c r="L22" t="n">
-        <v>5.4</v>
+        <v>5.83</v>
       </c>
       <c r="M22" t="n">
         <v>1.93</v>
@@ -1704,7 +1967,19 @@
         <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43187</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1731,28 +2006,28 @@
         <v>8.51</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43297</v>
+        <v>43298</v>
       </c>
       <c r="H23" t="n">
-        <v>481</v>
+        <v>510.05</v>
       </c>
       <c r="I23" t="n">
         <v>493.2605826999833</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K23" t="n">
-        <v>5.23</v>
+        <v>-0.49</v>
       </c>
       <c r="L23" t="n">
-        <v>1.13</v>
+        <v>1.49</v>
       </c>
       <c r="M23" t="n">
         <v>1.01</v>
       </c>
       <c r="N23" t="n">
-        <v>4.03</v>
+        <v>6.04</v>
       </c>
       <c r="O23" t="n">
         <v>-0.33</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43251</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -1788,28 +2075,28 @@
         <v>12.02</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43336</v>
+        <v>43339</v>
       </c>
       <c r="H24" t="n">
-        <v>564.65</v>
+        <v>520.75</v>
       </c>
       <c r="I24" t="n">
         <v>523.8268575088432</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="K24" t="n">
-        <v>10.7</v>
+        <v>2.1</v>
       </c>
       <c r="L24" t="n">
         <v>6.38</v>
       </c>
       <c r="M24" t="n">
-        <v>1.18</v>
+        <v>4.1</v>
       </c>
       <c r="N24" t="n">
-        <v>2.24</v>
+        <v>7.77</v>
       </c>
       <c r="O24" t="n">
         <v>6.04</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43307</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>11.77</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43418</v>
+        <v>43419</v>
       </c>
       <c r="H25" t="n">
-        <v>445.2</v>
+        <v>457.5</v>
       </c>
       <c r="I25" t="n">
         <v>446.9666827133626</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K25" t="n">
-        <v>14.51</v>
+        <v>12.15</v>
       </c>
       <c r="L25" t="n">
         <v>3.98</v>
@@ -1875,7 +2174,19 @@
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43342</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>4</v>
+      </c>
+      <c r="U25" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="26">
@@ -1902,28 +2213,28 @@
         <v>13.36</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43441</v>
+        <v>43444</v>
       </c>
       <c r="H26" t="n">
-        <v>430.65</v>
+        <v>411.35</v>
       </c>
       <c r="I26" t="n">
         <v>417.6944336852661</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K26" t="n">
-        <v>-5.87</v>
+        <v>-10.09</v>
       </c>
       <c r="L26" t="n">
-        <v>8.48</v>
+        <v>10.5</v>
       </c>
       <c r="M26" t="n">
-        <v>0.87</v>
+        <v>2.12</v>
       </c>
       <c r="N26" t="n">
-        <v>4.38</v>
+        <v>4.48</v>
       </c>
       <c r="O26" t="n">
         <v>2.76</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43433</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,28 +2282,28 @@
         <v>12.84</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43452</v>
+        <v>43453</v>
       </c>
       <c r="H27" t="n">
-        <v>456.15</v>
+        <v>477.15</v>
       </c>
       <c r="I27" t="n">
         <v>464.1600101060816</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K27" t="n">
-        <v>-10.89</v>
+        <v>-16</v>
       </c>
       <c r="L27" t="n">
-        <v>11.41</v>
+        <v>16.32</v>
       </c>
       <c r="M27" t="n">
-        <v>0.26</v>
+        <v>0.89</v>
       </c>
       <c r="N27" t="n">
-        <v>3.95</v>
+        <v>4.6</v>
       </c>
       <c r="O27" t="n">
         <v>-4.48</v>
@@ -1989,7 +2312,19 @@
         <v>1</v>
       </c>
       <c r="Q27" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43461</v>
+      </c>
+      <c r="S27" t="b">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2016,22 +2351,22 @@
         <v>11.81</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>43490</v>
+        <v>43493</v>
       </c>
       <c r="H28" t="n">
-        <v>444.55</v>
+        <v>438.2</v>
       </c>
       <c r="I28" t="n">
         <v>441.1690560219416</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="K28" t="n">
-        <v>-6.83</v>
+        <v>-8.16</v>
       </c>
       <c r="L28" t="n">
-        <v>7.71</v>
+        <v>9.15</v>
       </c>
       <c r="M28" t="n">
         <v>1.37</v>
@@ -2046,7 +2381,19 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>43461</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,22 +2420,22 @@
         <v>10.56</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>43529</v>
+        <v>43530</v>
       </c>
       <c r="H29" t="n">
-        <v>476.05</v>
+        <v>481.45</v>
       </c>
       <c r="I29" t="n">
         <v>479.4007501360369</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K29" t="n">
-        <v>-8.640000000000001</v>
+        <v>-9.869999999999999</v>
       </c>
       <c r="L29" t="n">
-        <v>10.11</v>
+        <v>10.92</v>
       </c>
       <c r="M29" t="n">
         <v>2.59</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>43496</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>3</v>
+      </c>
+      <c r="U29" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>8.74</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>43573</v>
+        <v>43577</v>
       </c>
       <c r="H30" t="n">
-        <v>508.95</v>
+        <v>495.8</v>
       </c>
       <c r="I30" t="n">
         <v>503.5556200811864</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="K30" t="n">
-        <v>5.71</v>
+        <v>2.98</v>
       </c>
       <c r="L30" t="n">
         <v>1.78</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>43552</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,28 +2558,28 @@
         <v>9.550000000000001</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>43602</v>
+        <v>43605</v>
       </c>
       <c r="H31" t="n">
-        <v>490.75</v>
+        <v>523.5</v>
       </c>
       <c r="I31" t="n">
         <v>510.998647560549</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K31" t="n">
-        <v>1.02</v>
+        <v>-5.59</v>
       </c>
       <c r="L31" t="n">
-        <v>3.21</v>
+        <v>6.27</v>
       </c>
       <c r="M31" t="n">
-        <v>0.5</v>
+        <v>2.23</v>
       </c>
       <c r="N31" t="n">
-        <v>3.2</v>
+        <v>6.67</v>
       </c>
       <c r="O31" t="n">
         <v>-2.58</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>43580</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>11.65</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>43663</v>
+        <v>43664</v>
       </c>
       <c r="H32" t="n">
-        <v>541.6</v>
+        <v>525.45</v>
       </c>
       <c r="I32" t="n">
         <v>527.6968261986444</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K32" t="n">
-        <v>3.46</v>
+        <v>0.37</v>
       </c>
       <c r="L32" t="n">
         <v>4.3</v>
@@ -2274,7 +2657,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>3</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>11.3</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>43728</v>
+        <v>43731</v>
       </c>
       <c r="H33" t="n">
-        <v>408.75</v>
+        <v>421.2</v>
       </c>
       <c r="I33" t="n">
         <v>417.2680074840026</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="K33" t="n">
-        <v>22.21</v>
+        <v>19.84</v>
       </c>
       <c r="L33" t="n">
         <v>3.05</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>43671</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>3</v>
+      </c>
+      <c r="U33" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -2358,22 +2765,22 @@
         <v>12.49</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>43735</v>
+        <v>43738</v>
       </c>
       <c r="H34" t="n">
-        <v>385.65</v>
+        <v>368.15</v>
       </c>
       <c r="I34" t="n">
         <v>368.5826639379579</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K34" t="n">
-        <v>-8.44</v>
+        <v>-12.59</v>
       </c>
       <c r="L34" t="n">
-        <v>9.18</v>
+        <v>14.17</v>
       </c>
       <c r="M34" t="n">
         <v>0.41</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>43734</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,22 +2834,22 @@
         <v>15.98</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>43768</v>
+        <v>43769</v>
       </c>
       <c r="H35" t="n">
-        <v>393.75</v>
+        <v>403.9</v>
       </c>
       <c r="I35" t="n">
         <v>398.5398193692967</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K35" t="n">
-        <v>-6.95</v>
+        <v>-9.710000000000001</v>
       </c>
       <c r="L35" t="n">
-        <v>8.34</v>
+        <v>10.7</v>
       </c>
       <c r="M35" t="n">
         <v>1.09</v>
@@ -2445,7 +2864,19 @@
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>43769</v>
+      </c>
+      <c r="S35" t="b">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>10.96</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>43833</v>
+        <v>43836</v>
       </c>
       <c r="H36" t="n">
-        <v>430.9</v>
+        <v>407.35</v>
       </c>
       <c r="I36" t="n">
         <v>415.0252002931476</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="K36" t="n">
-        <v>6.68</v>
+        <v>0.85</v>
       </c>
       <c r="L36" t="n">
         <v>1.83</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>43797</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>3</v>
+      </c>
+      <c r="U36" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -2529,22 +2972,22 @@
         <v>14.14</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>43845</v>
+        <v>43846</v>
       </c>
       <c r="H37" t="n">
-        <v>448.45</v>
+        <v>461.9</v>
       </c>
       <c r="I37" t="n">
         <v>451.6072977423458</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K37" t="n">
-        <v>-10.09</v>
+        <v>-13.39</v>
       </c>
       <c r="L37" t="n">
-        <v>10.7</v>
+        <v>14.35</v>
       </c>
       <c r="M37" t="n">
         <v>1.87</v>
@@ -2559,7 +3002,19 @@
         <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>43860</v>
+      </c>
+      <c r="S37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -2586,28 +3041,28 @@
         <v>10.43</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>43861</v>
+        <v>43862</v>
       </c>
       <c r="H38" t="n">
-        <v>429.2</v>
+        <v>393.8</v>
       </c>
       <c r="I38" t="n">
         <v>425.875765361922</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K38" t="n">
-        <v>-7.08</v>
+        <v>-14.74</v>
       </c>
       <c r="L38" t="n">
-        <v>9.83</v>
+        <v>16.09</v>
       </c>
       <c r="M38" t="n">
         <v>0.47</v>
       </c>
       <c r="N38" t="n">
-        <v>3.97</v>
+        <v>8.25</v>
       </c>
       <c r="O38" t="n">
         <v>3</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>43860</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>23.01</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>43937</v>
+        <v>43938</v>
       </c>
       <c r="H39" t="n">
-        <v>248.8</v>
+        <v>269.25</v>
       </c>
       <c r="I39" t="n">
         <v>268.0242910422678</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K39" t="n">
-        <v>36.82</v>
+        <v>31.63</v>
       </c>
       <c r="L39" t="n">
         <v>15.66</v>
@@ -2673,7 +3140,19 @@
         <v>1</v>
       </c>
       <c r="Q39" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>43888</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>3</v>
+      </c>
+      <c r="U39" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -2700,28 +3179,28 @@
         <v>28.33</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>43966</v>
+        <v>43969</v>
       </c>
       <c r="H40" t="n">
-        <v>245.4</v>
+        <v>211.65</v>
       </c>
       <c r="I40" t="n">
         <v>216.7197596889535</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="K40" t="n">
-        <v>-8.859999999999999</v>
+        <v>-21.39</v>
       </c>
       <c r="L40" t="n">
-        <v>11.46</v>
+        <v>21.75</v>
       </c>
       <c r="M40" t="n">
         <v>6.64</v>
       </c>
       <c r="N40" t="n">
-        <v>9.49</v>
+        <v>13.75</v>
       </c>
       <c r="O40" t="n">
         <v>8.220000000000001</v>
@@ -2730,7 +3209,19 @@
         <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>43951</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,22 +3248,22 @@
         <v>35.86</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>43998</v>
+        <v>43999</v>
       </c>
       <c r="H41" t="n">
-        <v>275.4</v>
+        <v>283.65</v>
       </c>
       <c r="I41" t="n">
         <v>278.57508009646</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K41" t="n">
-        <v>-30.12</v>
+        <v>-34.02</v>
       </c>
       <c r="L41" t="n">
-        <v>35.53</v>
+        <v>36.03</v>
       </c>
       <c r="M41" t="n">
         <v>2.76</v>
@@ -2787,7 +3278,19 @@
         <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>43979</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>19.01</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>44096</v>
+        <v>44097</v>
       </c>
       <c r="H42" t="n">
-        <v>278.1</v>
+        <v>269.55</v>
       </c>
       <c r="I42" t="n">
         <v>272.4574108587985</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K42" t="n">
-        <v>-1.96</v>
+        <v>-4.97</v>
       </c>
       <c r="L42" t="n">
         <v>13.1</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44007</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>4</v>
+      </c>
+      <c r="U42" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="43">
@@ -2871,28 +3386,28 @@
         <v>15.21</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>44112</v>
+        <v>44113</v>
       </c>
       <c r="H43" t="n">
-        <v>278.25</v>
+        <v>297.55</v>
       </c>
       <c r="I43" t="n">
         <v>295.9035873687634</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K43" t="n">
-        <v>-3.23</v>
+        <v>-10.39</v>
       </c>
       <c r="L43" t="n">
-        <v>5.75</v>
+        <v>14.67</v>
       </c>
       <c r="M43" t="n">
         <v>1.66</v>
       </c>
       <c r="N43" t="n">
-        <v>5.41</v>
+        <v>6.94</v>
       </c>
       <c r="O43" t="n">
         <v>-3.07</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>44098</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>14.71</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>44267</v>
+        <v>44270</v>
       </c>
       <c r="H44" t="n">
-        <v>421.45</v>
+        <v>411.3</v>
       </c>
       <c r="I44" t="n">
         <v>413.0569228718113</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="K44" t="n">
-        <v>41.64</v>
+        <v>38.23</v>
       </c>
       <c r="L44" t="n">
         <v>10.13</v>
@@ -2958,7 +3485,19 @@
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>107</v>
+        <v>108</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>44133</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>6</v>
+      </c>
+      <c r="U44" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>13.1</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>44323</v>
+        <v>44326</v>
       </c>
       <c r="H45" t="n">
-        <v>414.3</v>
+        <v>419.45</v>
       </c>
       <c r="I45" t="n">
         <v>416.6663991009013</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="K45" t="n">
-        <v>-0.73</v>
+        <v>-1.98</v>
       </c>
       <c r="L45" t="n">
         <v>3.45</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>44280</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>3</v>
+      </c>
+      <c r="U45" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>8.57</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>44364</v>
+        <v>44365</v>
       </c>
       <c r="H46" t="n">
-        <v>473.6</v>
+        <v>461.4</v>
       </c>
       <c r="I46" t="n">
         <v>469.6235613947582</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K46" t="n">
-        <v>12.91</v>
+        <v>10</v>
       </c>
       <c r="L46" t="n">
         <v>1.9</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>44343</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>12.99</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>44439</v>
+        <v>44440</v>
       </c>
       <c r="H47" t="n">
-        <v>393.75</v>
+        <v>399.75</v>
       </c>
       <c r="I47" t="n">
         <v>396.4890342384388</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K47" t="n">
-        <v>14.66</v>
+        <v>13.36</v>
       </c>
       <c r="L47" t="n">
         <v>3.6</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>44371</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>4</v>
+      </c>
+      <c r="U47" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="48">
@@ -3156,28 +3731,28 @@
         <v>8.220000000000001</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>44490</v>
+        <v>44491</v>
       </c>
       <c r="H48" t="n">
-        <v>431.5</v>
+        <v>400</v>
       </c>
       <c r="I48" t="n">
         <v>409.9224814106861</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K48" t="n">
-        <v>7.94</v>
+        <v>0.06</v>
       </c>
       <c r="L48" t="n">
         <v>3.16</v>
       </c>
       <c r="M48" t="n">
-        <v>1.02</v>
+        <v>5.56</v>
       </c>
       <c r="N48" t="n">
-        <v>3.26</v>
+        <v>7.3</v>
       </c>
       <c r="O48" t="n">
         <v>1.52</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>44469</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>11.98</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>44575</v>
+        <v>44578</v>
       </c>
       <c r="H49" t="n">
-        <v>370.4</v>
+        <v>381</v>
       </c>
       <c r="I49" t="n">
         <v>375.3479245552869</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="K49" t="n">
-        <v>7.4</v>
+        <v>4.75</v>
       </c>
       <c r="L49" t="n">
         <v>7.95</v>
@@ -3243,7 +3830,19 @@
         <v>1</v>
       </c>
       <c r="Q49" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>44497</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>4</v>
+      </c>
+      <c r="U49" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="50">
@@ -3270,28 +3869,28 @@
         <v>8.640000000000001</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>44581</v>
+        <v>44582</v>
       </c>
       <c r="H50" t="n">
-        <v>358.4</v>
+        <v>343.45</v>
       </c>
       <c r="I50" t="n">
         <v>348.0717439926004</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K50" t="n">
-        <v>-5.93</v>
+        <v>-9.859999999999999</v>
       </c>
       <c r="L50" t="n">
-        <v>6.82</v>
+        <v>10.73</v>
       </c>
       <c r="M50" t="n">
-        <v>0.01</v>
+        <v>0.86</v>
       </c>
       <c r="N50" t="n">
-        <v>2.86</v>
+        <v>4.17</v>
       </c>
       <c r="O50" t="n">
         <v>2.86</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S50" t="b">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>1</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -3327,28 +3938,28 @@
         <v>11.65</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>44588</v>
+        <v>44589</v>
       </c>
       <c r="H51" t="n">
-        <v>337</v>
+        <v>374.65</v>
       </c>
       <c r="I51" t="n">
         <v>368.0858374258285</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K51" t="n">
-        <v>1.88</v>
+        <v>-9.08</v>
       </c>
       <c r="L51" t="n">
-        <v>4.47</v>
+        <v>13.04</v>
       </c>
       <c r="M51" t="n">
-        <v>0.01</v>
+        <v>3.99</v>
       </c>
       <c r="N51" t="n">
-        <v>1.28</v>
+        <v>11.17</v>
       </c>
       <c r="O51" t="n">
         <v>-4.17</v>
@@ -3357,7 +3968,19 @@
         <v>1</v>
       </c>
       <c r="Q51" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,28 +4007,28 @@
         <v>15.72</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>44615</v>
+        <v>44616</v>
       </c>
       <c r="H52" t="n">
-        <v>354.55</v>
+        <v>321.6</v>
       </c>
       <c r="I52" t="n">
         <v>347.6521433650374</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K52" t="n">
-        <v>-5.37</v>
+        <v>-14.16</v>
       </c>
       <c r="L52" t="n">
-        <v>7.51</v>
+        <v>14.69</v>
       </c>
       <c r="M52" t="n">
         <v>3.94</v>
       </c>
       <c r="N52" t="n">
-        <v>8.390000000000001</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="O52" t="n">
         <v>11.17</v>
@@ -3414,7 +4037,19 @@
         <v>1</v>
       </c>
       <c r="Q52" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S52" t="b">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -3441,22 +4076,22 @@
         <v>19.69</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>44652</v>
+        <v>44655</v>
       </c>
       <c r="H53" t="n">
-        <v>363.75</v>
+        <v>376.7</v>
       </c>
       <c r="I53" t="n">
         <v>367.3829908522644</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="K53" t="n">
-        <v>-13.11</v>
+        <v>-17.13</v>
       </c>
       <c r="L53" t="n">
-        <v>13.5</v>
+        <v>18.22</v>
       </c>
       <c r="M53" t="n">
         <v>3.1</v>
@@ -3471,7 +4106,19 @@
         <v>1</v>
       </c>
       <c r="Q53" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,22 +4145,22 @@
         <v>11.04</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>44687</v>
+        <v>44690</v>
       </c>
       <c r="H54" t="n">
-        <v>355.4</v>
+        <v>341.65</v>
       </c>
       <c r="I54" t="n">
         <v>352.6365181442576</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K54" t="n">
-        <v>-5.65</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="L54" t="n">
-        <v>7.87</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="M54" t="n">
         <v>1.4</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3555,22 +4214,22 @@
         <v>13.63</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>44701</v>
+        <v>44704</v>
       </c>
       <c r="H55" t="n">
-        <v>361.4</v>
+        <v>365.45</v>
       </c>
       <c r="I55" t="n">
         <v>365.281948597004</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K55" t="n">
-        <v>-5.78</v>
+        <v>-6.97</v>
       </c>
       <c r="L55" t="n">
-        <v>7.1</v>
+        <v>7.64</v>
       </c>
       <c r="M55" t="n">
         <v>2.96</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S55" t="b">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>1</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -3612,22 +4283,22 @@
         <v>12.17</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>44720</v>
+        <v>44721</v>
       </c>
       <c r="H56" t="n">
-        <v>338.05</v>
+        <v>332.55</v>
       </c>
       <c r="I56" t="n">
         <v>336.5196229492395</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K56" t="n">
-        <v>-7.5</v>
+        <v>-9</v>
       </c>
       <c r="L56" t="n">
-        <v>7.78</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="M56" t="n">
         <v>1.23</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>10.18</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>44742</v>
+        <v>44743</v>
       </c>
       <c r="H57" t="n">
-        <v>318.85</v>
+        <v>329.75</v>
       </c>
       <c r="I57" t="n">
         <v>327.2235609973376</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K57" t="n">
-        <v>4.12</v>
+        <v>0.84</v>
       </c>
       <c r="L57" t="n">
         <v>1.37</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>12.1</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>44820</v>
+        <v>44823</v>
       </c>
       <c r="H58" t="n">
-        <v>422.1</v>
+        <v>405</v>
       </c>
       <c r="I58" t="n">
         <v>406.0876672945738</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="K58" t="n">
-        <v>28.01</v>
+        <v>22.82</v>
       </c>
       <c r="L58" t="n">
         <v>5.56</v>
@@ -3747,7 +4442,7 @@
         <v>2.89</v>
       </c>
       <c r="N58" t="n">
-        <v>3.53</v>
+        <v>4.05</v>
       </c>
       <c r="O58" t="n">
         <v>3.42</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>3</v>
+      </c>
+      <c r="U58" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>8.890000000000001</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>44897</v>
+        <v>44900</v>
       </c>
       <c r="H59" t="n">
-        <v>385.1</v>
+        <v>394.55</v>
       </c>
       <c r="I59" t="n">
         <v>390.2395938041847</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="K59" t="n">
-        <v>4.91</v>
+        <v>2.58</v>
       </c>
       <c r="L59" t="n">
         <v>3.83</v>
@@ -3813,7 +4520,19 @@
         <v>1</v>
       </c>
       <c r="Q59" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>4</v>
+      </c>
+      <c r="U59" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="60">
@@ -3840,22 +4559,22 @@
         <v>7.93</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>44951</v>
+        <v>44953</v>
       </c>
       <c r="H60" t="n">
-        <v>381.5</v>
+        <v>377.8</v>
       </c>
       <c r="I60" t="n">
         <v>379.897654469394</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="K60" t="n">
-        <v>-3.31</v>
+        <v>-4.25</v>
       </c>
       <c r="L60" t="n">
-        <v>4.16</v>
+        <v>5.92</v>
       </c>
       <c r="M60" t="n">
         <v>1.11</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>3</v>
+      </c>
+      <c r="U60" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>7.42</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45043</v>
+        <v>45044</v>
       </c>
       <c r="H61" t="n">
-        <v>331.25</v>
+        <v>335.7</v>
       </c>
       <c r="I61" t="n">
         <v>335.114650312167</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K61" t="n">
-        <v>12.32</v>
+        <v>11.14</v>
       </c>
       <c r="L61" t="n">
         <v>5.86</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>4</v>
+      </c>
+      <c r="U61" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>6.28</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45224</v>
+        <v>45225</v>
       </c>
       <c r="H62" t="n">
-        <v>447</v>
+        <v>437.85</v>
       </c>
       <c r="I62" t="n">
         <v>444.9285703591454</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="K62" t="n">
-        <v>33.15</v>
+        <v>30.43</v>
       </c>
       <c r="L62" t="n">
         <v>1.62</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>123</v>
+        <v>124</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>6</v>
+      </c>
+      <c r="U62" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="63">
@@ -4011,28 +4766,28 @@
         <v>7.6</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="H63" t="n">
-        <v>457.7</v>
+        <v>478.7</v>
       </c>
       <c r="I63" t="n">
         <v>471.1158343397654</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K63" t="n">
-        <v>-4.53</v>
+        <v>-9.33</v>
       </c>
       <c r="L63" t="n">
-        <v>8.130000000000001</v>
+        <v>9.73</v>
       </c>
       <c r="M63" t="n">
         <v>1.24</v>
       </c>
       <c r="N63" t="n">
-        <v>3.42</v>
+        <v>4.59</v>
       </c>
       <c r="O63" t="n">
         <v>-2.05</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S63" t="b">
+        <v>0</v>
+      </c>
+      <c r="T63" t="n">
+        <v>1</v>
+      </c>
+      <c r="U63" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>8.56</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45363</v>
+        <v>45364</v>
       </c>
       <c r="H64" t="n">
-        <v>624.1</v>
+        <v>590.45</v>
       </c>
       <c r="I64" t="n">
         <v>614.8414130442166</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K64" t="n">
-        <v>30.37</v>
+        <v>23.34</v>
       </c>
       <c r="L64" t="n">
         <v>4.32</v>
@@ -4089,7 +4856,7 @@
         <v>1.63</v>
       </c>
       <c r="N64" t="n">
-        <v>4.58</v>
+        <v>5.39</v>
       </c>
       <c r="O64" t="n">
         <v>4.59</v>
@@ -4098,7 +4865,19 @@
         <v>1</v>
       </c>
       <c r="Q64" t="n">
-        <v>73</v>
+        <v>74</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>5</v>
+      </c>
+      <c r="U64" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="65">
@@ -4125,28 +4904,28 @@
         <v>12.23</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>45379</v>
+        <v>45383</v>
       </c>
       <c r="H65" t="n">
-        <v>610.95</v>
+        <v>636.2</v>
       </c>
       <c r="I65" t="n">
         <v>619.7422679008203</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="K65" t="n">
-        <v>-3.47</v>
+        <v>-7.75</v>
       </c>
       <c r="L65" t="n">
-        <v>6.01</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="M65" t="n">
-        <v>0.9</v>
+        <v>1.05</v>
       </c>
       <c r="N65" t="n">
-        <v>3.74</v>
+        <v>4.13</v>
       </c>
       <c r="O65" t="n">
         <v>-5.39</v>
@@ -4155,7 +4934,19 @@
         <v>1</v>
       </c>
       <c r="Q65" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -4182,19 +4973,19 @@
         <v>9.85</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>45420</v>
+        <v>45421</v>
       </c>
       <c r="H66" t="n">
-        <v>635.6</v>
+        <v>620.1</v>
       </c>
       <c r="I66" t="n">
         <v>620.7555447581007</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K66" t="n">
-        <v>-0.09</v>
+        <v>-2.53</v>
       </c>
       <c r="L66" t="n">
         <v>3.47</v>
@@ -4212,7 +5003,19 @@
         <v>1</v>
       </c>
       <c r="Q66" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>2</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -4239,22 +5042,22 @@
         <v>12.06</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>45454</v>
+        <v>45455</v>
       </c>
       <c r="H67" t="n">
-        <v>680.1</v>
+        <v>715.4</v>
       </c>
       <c r="I67" t="n">
         <v>703.5239284660632</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K67" t="n">
-        <v>-9.68</v>
+        <v>-15.37</v>
       </c>
       <c r="L67" t="n">
-        <v>10.95</v>
+        <v>16.04</v>
       </c>
       <c r="M67" t="n">
         <v>5.9</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -4296,28 +5111,28 @@
         <v>14.77</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>45506</v>
+        <v>45509</v>
       </c>
       <c r="H68" t="n">
-        <v>748.6</v>
+        <v>686.15</v>
       </c>
       <c r="I68" t="n">
         <v>738.0427880571191</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="K68" t="n">
-        <v>4.64</v>
+        <v>-4.09</v>
       </c>
       <c r="L68" t="n">
-        <v>4.65</v>
+        <v>6.49</v>
       </c>
       <c r="M68" t="n">
-        <v>1.66</v>
+        <v>5.11</v>
       </c>
       <c r="N68" t="n">
-        <v>3.03</v>
+        <v>8.34</v>
       </c>
       <c r="O68" t="n">
         <v>5.19</v>
@@ -4326,7 +5141,19 @@
         <v>1</v>
       </c>
       <c r="Q68" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>3</v>
+      </c>
+      <c r="U68" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="69">
@@ -4353,25 +5180,25 @@
         <v>14.95</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>45547</v>
+        <v>45548</v>
       </c>
       <c r="H69" t="n">
-        <v>703.7</v>
+        <v>723.3</v>
       </c>
       <c r="I69" t="n">
         <v>719.7664775487726</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K69" t="n">
-        <v>-2.56</v>
+        <v>-5.41</v>
       </c>
       <c r="L69" t="n">
-        <v>5.52</v>
+        <v>6.51</v>
       </c>
       <c r="M69" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="N69" t="n">
         <v>4.05</v>
@@ -4383,7 +5210,19 @@
         <v>1</v>
       </c>
       <c r="Q69" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>2</v>
+      </c>
+      <c r="U69" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -4410,25 +5249,25 @@
         <v>10.07</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>45566</v>
+        <v>45568</v>
       </c>
       <c r="H70" t="n">
-        <v>659.25</v>
+        <v>636.6</v>
       </c>
       <c r="I70" t="n">
         <v>650.4502035062085</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K70" t="n">
-        <v>-8.859999999999999</v>
+        <v>-11.99</v>
       </c>
       <c r="L70" t="n">
-        <v>10.96</v>
+        <v>12.89</v>
       </c>
       <c r="M70" t="n">
-        <v>0.05</v>
+        <v>0.66</v>
       </c>
       <c r="N70" t="n">
         <v>5.88</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>2</v>
+      </c>
+      <c r="U70" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -4467,19 +5318,19 @@
         <v>10.07</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>45687</v>
+        <v>45688</v>
       </c>
       <c r="H71" t="n">
-        <v>584.35</v>
+        <v>598.1</v>
       </c>
       <c r="I71" t="n">
         <v>593.4566574163194</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K71" t="n">
-        <v>8.210000000000001</v>
+        <v>6.05</v>
       </c>
       <c r="L71" t="n">
         <v>3.3</v>
@@ -4497,7 +5348,19 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>83</v>
+        <v>84</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>5</v>
+      </c>
+      <c r="U71" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="72">
@@ -4524,19 +5387,19 @@
         <v>11.3</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>45705</v>
+        <v>45706</v>
       </c>
       <c r="H72" t="n">
-        <v>538.5</v>
+        <v>530.55</v>
       </c>
       <c r="I72" t="n">
         <v>532.2843921655963</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K72" t="n">
-        <v>-9.960000000000001</v>
+        <v>-11.29</v>
       </c>
       <c r="L72" t="n">
         <v>13.23</v>
@@ -4554,7 +5417,19 @@
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S72" t="b">
+        <v>0</v>
+      </c>
+      <c r="T72" t="n">
+        <v>1</v>
+      </c>
+      <c r="U72" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -4581,22 +5456,22 @@
         <v>11.11</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>45734</v>
+        <v>45735</v>
       </c>
       <c r="H73" t="n">
-        <v>539.8</v>
+        <v>549.8</v>
       </c>
       <c r="I73" t="n">
         <v>546.1541292208719</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K73" t="n">
-        <v>-1.74</v>
+        <v>-3.63</v>
       </c>
       <c r="L73" t="n">
-        <v>3.74</v>
+        <v>4.59</v>
       </c>
       <c r="M73" t="n">
         <v>1.95</v>
@@ -4611,7 +5486,19 @@
         <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S73" t="b">
+        <v>1</v>
+      </c>
+      <c r="T73" t="n">
+        <v>2</v>
+      </c>
+      <c r="U73" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -4638,19 +5525,19 @@
         <v>10.15</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>45863</v>
+        <v>45866</v>
       </c>
       <c r="H74" t="n">
-        <v>606.9</v>
+        <v>590.3</v>
       </c>
       <c r="I74" t="n">
         <v>603.7638916604699</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="K74" t="n">
-        <v>10.39</v>
+        <v>7.37</v>
       </c>
       <c r="L74" t="n">
         <v>4.94</v>
@@ -4668,7 +5555,19 @@
         <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>88</v>
+        <v>89</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S74" t="b">
+        <v>1</v>
+      </c>
+      <c r="T74" t="n">
+        <v>5</v>
+      </c>
+      <c r="U74" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="75">
@@ -4695,19 +5594,19 @@
         <v>8.81</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>45917</v>
+        <v>45918</v>
       </c>
       <c r="H75" t="n">
-        <v>572</v>
+        <v>593.2</v>
       </c>
       <c r="I75" t="n">
         <v>585.4136441593791</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K75" t="n">
-        <v>3.1</v>
+        <v>-0.49</v>
       </c>
       <c r="L75" t="n">
         <v>3.75</v>
@@ -4716,7 +5615,7 @@
         <v>1.32</v>
       </c>
       <c r="N75" t="n">
-        <v>3.65</v>
+        <v>3.71</v>
       </c>
       <c r="O75" t="n">
         <v>-2.74</v>
@@ -4725,7 +5624,19 @@
         <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R75" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S75" t="b">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>3</v>
+      </c>
+      <c r="U75" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="76">
@@ -4752,22 +5663,22 @@
         <v>6.48</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>45937</v>
+        <v>45938</v>
       </c>
       <c r="H76" t="n">
-        <v>566.65</v>
+        <v>562.05</v>
       </c>
       <c r="I76" t="n">
         <v>562.3601252791212</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K76" t="n">
-        <v>-4.48</v>
+        <v>-5.25</v>
       </c>
       <c r="L76" t="n">
-        <v>5.15</v>
+        <v>5.34</v>
       </c>
       <c r="M76" t="n">
         <v>0.39</v>
@@ -4782,7 +5693,19 @@
         <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R76" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S76" t="b">
+        <v>1</v>
+      </c>
+      <c r="T76" t="n">
+        <v>2</v>
+      </c>
+      <c r="U76" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="77">
@@ -4809,22 +5732,22 @@
         <v>6.32</v>
       </c>
       <c r="G77" s="1" t="n">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="H77" t="n">
-        <v>585.9</v>
+        <v>593.45</v>
       </c>
       <c r="I77" t="n">
         <v>592.4622554864761</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K77" t="n">
-        <v>-4.24</v>
+        <v>-5.59</v>
       </c>
       <c r="L77" t="n">
-        <v>4.79</v>
+        <v>5.84</v>
       </c>
       <c r="M77" t="n">
         <v>0.7</v>
@@ -4839,7 +5762,19 @@
         <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R77" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S77" t="b">
+        <v>1</v>
+      </c>
+      <c r="T77" t="n">
+        <v>2</v>
+      </c>
+      <c r="U77" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="78">
@@ -4866,22 +5801,22 @@
         <v>5.18</v>
       </c>
       <c r="G78" s="1" t="n">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="H78" t="n">
-        <v>563.6</v>
+        <v>554.8</v>
       </c>
       <c r="I78" t="n">
         <v>562.7029081179244</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K78" t="n">
-        <v>-5.03</v>
+        <v>-6.51</v>
       </c>
       <c r="L78" t="n">
-        <v>5.45</v>
+        <v>6.82</v>
       </c>
       <c r="M78" t="n">
         <v>0.46</v>
@@ -4896,7 +5831,19 @@
         <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R78" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S78" t="b">
+        <v>0</v>
+      </c>
+      <c r="T78" t="n">
+        <v>1</v>
+      </c>
+      <c r="U78" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -4923,19 +5870,19 @@
         <v>5.46</v>
       </c>
       <c r="G79" s="1" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="H79" t="n">
-        <v>532.05</v>
+        <v>547</v>
       </c>
       <c r="I79" t="n">
         <v>540.8301880233106</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K79" t="n">
-        <v>4.1</v>
+        <v>1.41</v>
       </c>
       <c r="L79" t="n">
         <v>2.2</v>
@@ -4944,7 +5891,7 @@
         <v>2.95</v>
       </c>
       <c r="N79" t="n">
-        <v>2.73</v>
+        <v>2.81</v>
       </c>
       <c r="O79" t="n">
         <v>-1.56</v>
@@ -4953,7 +5900,19 @@
         <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>67</v>
+        <v>68</v>
+      </c>
+      <c r="R79" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S79" t="b">
+        <v>1</v>
+      </c>
+      <c r="T79" t="n">
+        <v>5</v>
+      </c>
+      <c r="U79" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="80">
@@ -4980,28 +5939,28 @@
         <v>7.8</v>
       </c>
       <c r="G80" s="1" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="H80" t="n">
-        <v>511.8</v>
+        <v>500.2</v>
       </c>
       <c r="I80" t="n">
         <v>508.8729204950419</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K80" t="n">
-        <v>-6.44</v>
+        <v>-8.56</v>
       </c>
       <c r="L80" t="n">
-        <v>6.65</v>
+        <v>10.47</v>
       </c>
       <c r="M80" t="n">
-        <v>2.37</v>
+        <v>2.63</v>
       </c>
       <c r="N80" t="n">
-        <v>1.88</v>
+        <v>2.27</v>
       </c>
       <c r="O80" t="n">
         <v>2.81</v>
@@ -5010,7 +5969,19 @@
         <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R80" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S80" t="b">
+        <v>0</v>
+      </c>
+      <c r="T80" t="n">
+        <v>1</v>
+      </c>
+      <c r="U80" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="81">
@@ -5037,22 +6008,22 @@
         <v>7.46</v>
       </c>
       <c r="G81" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="H81" t="n">
-        <v>512.85</v>
+        <v>529.6</v>
       </c>
       <c r="I81" t="n">
         <v>518.1204357284778</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K81" t="n">
-        <v>-2.53</v>
+        <v>-5.88</v>
       </c>
       <c r="L81" t="n">
-        <v>4.35</v>
+        <v>6.06</v>
       </c>
       <c r="M81" t="n">
         <v>3.18</v>
@@ -5067,7 +6038,19 @@
         <v>0</v>
       </c>
       <c r="Q81" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R81" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S81" t="b">
+        <v>1</v>
+      </c>
+      <c r="T81" t="n">
+        <v>2</v>
+      </c>
+      <c r="U81" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="82">
@@ -5094,19 +6077,19 @@
         <v>9.92</v>
       </c>
       <c r="G82" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="H82" t="n">
-        <v>546.8</v>
+        <v>537.95</v>
       </c>
       <c r="I82" t="n">
         <v>541.1831216075832</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K82" t="n">
-        <v>3.25</v>
+        <v>1.58</v>
       </c>
       <c r="L82" t="n">
         <v>3.1</v>
@@ -5124,7 +6107,19 @@
         <v>0</v>
       </c>
       <c r="Q82" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R82" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S82" t="b">
+        <v>1</v>
+      </c>
+      <c r="T82" t="n">
+        <v>2</v>
+      </c>
+      <c r="U82" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="83">
@@ -5151,19 +6146,19 @@
         <v>10.83</v>
       </c>
       <c r="G83" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="H83" t="n">
-        <v>506</v>
+        <v>524.4</v>
       </c>
       <c r="I83" t="n">
         <v>522.6455468099397</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K83" t="n">
-        <v>5.94</v>
+        <v>2.52</v>
       </c>
       <c r="L83" t="n">
         <v>6.1</v>
@@ -5181,7 +6176,19 @@
         <v>0</v>
       </c>
       <c r="Q83" t="n">
-        <v>67</v>
+        <v>68</v>
+      </c>
+      <c r="R83" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S83" t="b">
+        <v>1</v>
+      </c>
+      <c r="T83" t="n">
+        <v>5</v>
+      </c>
+      <c r="U83" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="84">
@@ -5208,28 +6215,28 @@
         <v>8.23</v>
       </c>
       <c r="G84" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="H84" t="n">
-        <v>530.2</v>
+        <v>509</v>
       </c>
       <c r="I84" t="n">
         <v>523.3342299899401</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K84" t="n">
-        <v>1.11</v>
+        <v>-2.94</v>
       </c>
       <c r="L84" t="n">
-        <v>3.51</v>
+        <v>4.8</v>
       </c>
       <c r="M84" t="n">
         <v>1.14</v>
       </c>
       <c r="N84" t="n">
-        <v>3.71</v>
+        <v>4</v>
       </c>
       <c r="O84" t="n">
         <v>3.64</v>
@@ -5238,7 +6245,19 @@
         <v>0</v>
       </c>
       <c r="Q84" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R84" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S84" t="b">
+        <v>1</v>
+      </c>
+      <c r="T84" t="n">
+        <v>2</v>
+      </c>
+      <c r="U84" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="85">
@@ -5265,22 +6284,22 @@
         <v>12.38</v>
       </c>
       <c r="G85" s="1" t="n">
-        <v>46304</v>
+        <v>46307</v>
       </c>
       <c r="H85" t="n">
-        <v>551.65</v>
+        <v>568</v>
       </c>
       <c r="I85" t="n">
         <v>555.1372420332402</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K85" t="n">
-        <v>-8.380000000000001</v>
+        <v>-11.59</v>
       </c>
       <c r="L85" t="n">
-        <v>8.91</v>
+        <v>11.59</v>
       </c>
       <c r="M85" t="n">
         <v>0.88</v>
@@ -5295,7 +6314,19 @@
         <v>0</v>
       </c>
       <c r="Q85" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R85" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S85" t="b">
+        <v>0</v>
+      </c>
+      <c r="T85" t="n">
+        <v>1</v>
+      </c>
+      <c r="U85" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -5322,22 +6353,22 @@
         <v>11.84</v>
       </c>
       <c r="G86" s="1" t="n">
-        <v>46314</v>
+        <v>46316</v>
       </c>
       <c r="H86" t="n">
-        <v>511.5</v>
+        <v>503.75</v>
       </c>
       <c r="I86" t="n">
         <v>503.784444451792</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K86" t="n">
-        <v>-9.949999999999999</v>
+        <v>-11.31</v>
       </c>
       <c r="L86" t="n">
-        <v>10.07</v>
+        <v>11.68</v>
       </c>
       <c r="M86" t="n">
         <v>1.23</v>
@@ -5352,7 +6383,19 @@
         <v>0</v>
       </c>
       <c r="Q86" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R86" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S86" t="b">
+        <v>0</v>
+      </c>
+      <c r="T86" t="n">
+        <v>1</v>
+      </c>
+      <c r="U86" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="87">
@@ -5403,6 +6446,14 @@
       <c r="Q87" t="n">
         <v>6</v>
       </c>
+      <c r="R87" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S87" t="b">
+        <v>1</v>
+      </c>
+      <c r="T87" t="inlineStr"/>
+      <c r="U87" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10361,7 +11412,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>48.8</v>
+        <v>50.6</v>
       </c>
     </row>
     <row r="6">
@@ -10371,7 +11422,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7">
@@ -10381,7 +11432,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="8">
@@ -10391,7 +11442,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -10401,7 +11452,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="10">
@@ -10411,7 +11462,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="11">
@@ -10421,7 +11472,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12">
@@ -10431,7 +11482,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13">
@@ -10441,7 +11492,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>38.8</v>
+        <v>36.5</v>
       </c>
     </row>
     <row r="14">
@@ -10451,7 +11502,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.75</v>
+        <v>-1.69</v>
       </c>
     </row>
     <row r="15">
@@ -10461,7 +11512,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.76</v>
+        <v>-0.89</v>
       </c>
     </row>
     <row r="16">
@@ -10471,7 +11522,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.71</v>
+        <v>-2.51</v>
       </c>
     </row>
     <row r="17">
@@ -10481,7 +11532,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>41.64</v>
+        <v>38.23</v>
       </c>
     </row>
     <row r="18">
@@ -10491,7 +11542,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>45.9</v>
+        <v>36.5</v>
       </c>
     </row>
     <row r="19">
@@ -10501,7 +11552,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>6.33</v>
+        <v>7.73</v>
       </c>
     </row>
     <row r="20">
@@ -10511,7 +11562,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5.25</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="21">
@@ -10521,7 +11572,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>35.53</v>
+        <v>36.03</v>
       </c>
     </row>
     <row r="22">
@@ -10531,7 +11582,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>46</v>
+        <v>53</v>
       </c>
     </row>
     <row r="23">
@@ -10541,7 +11592,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
     </row>
     <row r="24">
@@ -10551,7 +11602,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.74</v>
+        <v>1.98</v>
       </c>
     </row>
     <row r="25">
@@ -10571,7 +11622,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4.47</v>
+        <v>5.05</v>
       </c>
     </row>
     <row r="27">
@@ -10591,7 +11642,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>42</v>
+        <v>53</v>
       </c>
     </row>
     <row r="29">
